--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/124.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/124.xlsx
@@ -426,13 +426,13 @@
         <v>-7.91964306368257</v>
       </c>
       <c r="E2">
-        <v>-23.73564989541319</v>
+        <v>-27.94822208478247</v>
       </c>
       <c r="F2">
-        <v>-2.975451126263581</v>
+        <v>-3.072276506874607</v>
       </c>
       <c r="G2">
-        <v>-12.33341207285883</v>
+        <v>-15.4758928020106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.965188514051767</v>
       </c>
       <c r="E3">
-        <v>-24.17322728182636</v>
+        <v>-27.74548230345907</v>
       </c>
       <c r="F3">
-        <v>-2.808715678693291</v>
+        <v>-3.066880521612771</v>
       </c>
       <c r="G3">
-        <v>-12.36826549629627</v>
+        <v>-15.48616211427342</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.009789278249832</v>
       </c>
       <c r="E4">
-        <v>-23.66662236611427</v>
+        <v>-27.82145651188575</v>
       </c>
       <c r="F4">
-        <v>-2.886713096606087</v>
+        <v>-3.079239763262539</v>
       </c>
       <c r="G4">
-        <v>-12.23756184786031</v>
+        <v>-15.38661897572585</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.042697899841977</v>
       </c>
       <c r="E5">
-        <v>-24.01912783981935</v>
+        <v>-28.82457690322085</v>
       </c>
       <c r="F5">
-        <v>-2.879540263265246</v>
+        <v>-3.094530597150815</v>
       </c>
       <c r="G5">
-        <v>-12.29339750892566</v>
+        <v>-15.37841544387953</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.046757179637234</v>
       </c>
       <c r="E6">
-        <v>-24.58648223434433</v>
+        <v>-28.77778418129959</v>
       </c>
       <c r="F6">
-        <v>-2.986962948060286</v>
+        <v>-3.222111602692981</v>
       </c>
       <c r="G6">
-        <v>-11.86819766095274</v>
+        <v>-15.05734052948055</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.013127673867924</v>
       </c>
       <c r="E7">
-        <v>-25.22610654555773</v>
+        <v>-29.80187820000121</v>
       </c>
       <c r="F7">
-        <v>-2.841621745402098</v>
+        <v>-3.192196770675682</v>
       </c>
       <c r="G7">
-        <v>-11.73185946400894</v>
+        <v>-15.10164556043261</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.929623683179744</v>
       </c>
       <c r="E8">
-        <v>-24.83846011355314</v>
+        <v>-29.28008704670439</v>
       </c>
       <c r="F8">
-        <v>-2.691833866525683</v>
+        <v>-2.874714194776536</v>
       </c>
       <c r="G8">
-        <v>-11.56045596871317</v>
+        <v>-14.66372328595228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.775438322457185</v>
       </c>
       <c r="E9">
-        <v>-26.3403783314111</v>
+        <v>-30.18301947909378</v>
       </c>
       <c r="F9">
-        <v>-2.713426091247055</v>
+        <v>-2.995837248046477</v>
       </c>
       <c r="G9">
-        <v>-11.57503561126812</v>
+        <v>-14.43022719852195</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.535212909806539</v>
       </c>
       <c r="E10">
-        <v>-26.03158621730206</v>
+        <v>-30.43301615092423</v>
       </c>
       <c r="F10">
-        <v>-2.890511989515325</v>
+        <v>-2.952729836772193</v>
       </c>
       <c r="G10">
-        <v>-11.21705970101565</v>
+        <v>-14.35301700018229</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.203703706299113</v>
       </c>
       <c r="E11">
-        <v>-26.85281139317106</v>
+        <v>-31.0685512501087</v>
       </c>
       <c r="F11">
-        <v>-2.750531980688056</v>
+        <v>-2.963815877723859</v>
       </c>
       <c r="G11">
-        <v>-10.89438744839397</v>
+        <v>-13.91032091903433</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.776690049467701</v>
       </c>
       <c r="E12">
-        <v>-27.41659282170399</v>
+        <v>-31.44891816014597</v>
       </c>
       <c r="F12">
-        <v>-2.781213880920347</v>
+        <v>-2.969305468502211</v>
       </c>
       <c r="G12">
-        <v>-11.02652787359398</v>
+        <v>-13.86884640451834</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.256750883844786</v>
       </c>
       <c r="E13">
-        <v>-28.03879609340989</v>
+        <v>-31.55424593709037</v>
       </c>
       <c r="F13">
-        <v>-2.89134201365293</v>
+        <v>-2.942085315646219</v>
       </c>
       <c r="G13">
-        <v>-10.84495438240157</v>
+        <v>-13.55254198624145</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.669006432024786</v>
       </c>
       <c r="E14">
-        <v>-28.73141713593505</v>
+        <v>-31.86296785985229</v>
       </c>
       <c r="F14">
-        <v>-2.553455920255429</v>
+        <v>-2.961324976943641</v>
       </c>
       <c r="G14">
-        <v>-9.952706080293817</v>
+        <v>-13.26206313371641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.037463674785577</v>
       </c>
       <c r="E15">
-        <v>-29.48951311990012</v>
+        <v>-33.23620948878229</v>
       </c>
       <c r="F15">
-        <v>-2.203633052583586</v>
+        <v>-2.612749630580415</v>
       </c>
       <c r="G15">
-        <v>-9.860192885198883</v>
+        <v>-12.64949302931182</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.386406460025547</v>
       </c>
       <c r="E16">
-        <v>-30.05500404737095</v>
+        <v>-33.42066329206273</v>
       </c>
       <c r="F16">
-        <v>-2.39611581576769</v>
+        <v>-2.612221960544831</v>
       </c>
       <c r="G16">
-        <v>-9.458815722926566</v>
+        <v>-12.25261489842737</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.749711118032983</v>
       </c>
       <c r="E17">
-        <v>-30.62519779509875</v>
+        <v>-34.17104502055572</v>
       </c>
       <c r="F17">
-        <v>-2.05513494175333</v>
+        <v>-2.701933321900615</v>
       </c>
       <c r="G17">
-        <v>-8.905302440397042</v>
+        <v>-12.48458813490965</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.153224094202368</v>
       </c>
       <c r="E18">
-        <v>-31.53552522554267</v>
+        <v>-34.77459324358702</v>
       </c>
       <c r="F18">
-        <v>-1.986707652445077</v>
+        <v>-2.575200564578916</v>
       </c>
       <c r="G18">
-        <v>-8.807939296087076</v>
+        <v>-11.73603075138842</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.612219982517487</v>
       </c>
       <c r="E19">
-        <v>-32.13345134809344</v>
+        <v>-35.71274135409706</v>
       </c>
       <c r="F19">
-        <v>-1.891629298686555</v>
+        <v>-2.331489076103482</v>
       </c>
       <c r="G19">
-        <v>-8.343019522733988</v>
+        <v>-11.77297312906115</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.142192738284697</v>
       </c>
       <c r="E20">
-        <v>-32.63553231827186</v>
+        <v>-36.40787569969648</v>
       </c>
       <c r="F20">
-        <v>-1.639100667575723</v>
+        <v>-2.228529634874725</v>
       </c>
       <c r="G20">
-        <v>-8.109467156029483</v>
+        <v>-11.85799787014625</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.752901565333419</v>
       </c>
       <c r="E21">
-        <v>-33.70480692214801</v>
+        <v>-36.57403673222293</v>
       </c>
       <c r="F21">
-        <v>-1.747214210784698</v>
+        <v>-2.172293428633473</v>
       </c>
       <c r="G21">
-        <v>-8.201894276940395</v>
+        <v>-11.48148952596494</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.443437960909361</v>
       </c>
       <c r="E22">
-        <v>-34.23132127383482</v>
+        <v>-37.11845440589907</v>
       </c>
       <c r="F22">
-        <v>-1.486887328943911</v>
+        <v>-1.841861813493764</v>
       </c>
       <c r="G22">
-        <v>-8.204354012276074</v>
+        <v>-11.47970514191927</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.210737228817313</v>
       </c>
       <c r="E23">
-        <v>-34.02783429430016</v>
+        <v>-37.98353332405834</v>
       </c>
       <c r="F23">
-        <v>-1.196885841632638</v>
+        <v>-1.933871894392316</v>
       </c>
       <c r="G23">
-        <v>-7.97816429885091</v>
+        <v>-11.34617428759277</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.055250869127175</v>
       </c>
       <c r="E24">
-        <v>-34.78489325771746</v>
+        <v>-37.77821231255057</v>
       </c>
       <c r="F24">
-        <v>-1.423737568358894</v>
+        <v>-1.551916655165881</v>
       </c>
       <c r="G24">
-        <v>-7.997434984435007</v>
+        <v>-11.20696584766641</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9698087340005628</v>
       </c>
       <c r="E25">
-        <v>-35.61687129511768</v>
+        <v>-37.97693080895516</v>
       </c>
       <c r="F25">
-        <v>-1.000483243898486</v>
+        <v>-1.479303625371282</v>
       </c>
       <c r="G25">
-        <v>-7.749749898823355</v>
+        <v>-11.58391118385891</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9448661687637808</v>
       </c>
       <c r="E26">
-        <v>-35.39539948106155</v>
+        <v>-38.5501631627421</v>
       </c>
       <c r="F26">
-        <v>-1.105228645247678</v>
+        <v>-1.515592744553122</v>
       </c>
       <c r="G26">
-        <v>-7.942062799745158</v>
+        <v>-11.51148968964181</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.9804665778170264</v>
       </c>
       <c r="E27">
-        <v>-35.37741917501409</v>
+        <v>-38.35653240688513</v>
       </c>
       <c r="F27">
-        <v>-0.9557878523130361</v>
+        <v>-1.533264306357044</v>
       </c>
       <c r="G27">
-        <v>-7.739417686195289</v>
+        <v>-11.39707392525906</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.070850021437624</v>
       </c>
       <c r="E28">
-        <v>-34.62943300927115</v>
+        <v>-38.23130877938803</v>
       </c>
       <c r="F28">
-        <v>-1.14179029730504</v>
+        <v>-1.390373414476338</v>
       </c>
       <c r="G28">
-        <v>-7.943857115427443</v>
+        <v>-11.8105080943854</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.206603371195155</v>
       </c>
       <c r="E29">
-        <v>-35.24492055402366</v>
+        <v>-38.47162583802708</v>
       </c>
       <c r="F29">
-        <v>-0.710799849669888</v>
+        <v>-1.497976683365188</v>
       </c>
       <c r="G29">
-        <v>-8.208717311296834</v>
+        <v>-11.5760618803853</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.387108311265501</v>
       </c>
       <c r="E30">
-        <v>-35.20190457942481</v>
+        <v>-38.19159179810375</v>
       </c>
       <c r="F30">
-        <v>-0.6425937344581822</v>
+        <v>-1.305052400355392</v>
       </c>
       <c r="G30">
-        <v>-7.952421496737538</v>
+        <v>-11.47361373812701</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.609827478644264</v>
       </c>
       <c r="E31">
-        <v>-34.41039524999414</v>
+        <v>-37.88810479129471</v>
       </c>
       <c r="F31">
-        <v>-0.8939402852852194</v>
+        <v>-1.352892274601869</v>
       </c>
       <c r="G31">
-        <v>-8.225336249903975</v>
+        <v>-11.84808278625613</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.866947327722338</v>
       </c>
       <c r="E32">
-        <v>-34.37334327566338</v>
+        <v>-37.67305661761846</v>
       </c>
       <c r="F32">
-        <v>-0.9419855946475908</v>
+        <v>-1.547334955060997</v>
       </c>
       <c r="G32">
-        <v>-8.338123225881406</v>
+        <v>-11.94932920048366</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.157432554700262</v>
       </c>
       <c r="E33">
-        <v>-34.53968318291313</v>
+        <v>-37.34696346856312</v>
       </c>
       <c r="F33">
-        <v>-0.9398334961351177</v>
+        <v>-1.534752882579875</v>
       </c>
       <c r="G33">
-        <v>-8.624756879762584</v>
+        <v>-11.7423770671872</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.478857958153454</v>
       </c>
       <c r="E34">
-        <v>-33.98497455205456</v>
+        <v>-37.03238170043528</v>
       </c>
       <c r="F34">
-        <v>-0.829703706667729</v>
+        <v>-1.283243971741889</v>
       </c>
       <c r="G34">
-        <v>-9.403681897515543</v>
+        <v>-12.21038889007397</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.823310314119397</v>
       </c>
       <c r="E35">
-        <v>-32.76684900754629</v>
+        <v>-36.71426092987044</v>
       </c>
       <c r="F35">
-        <v>-0.9635861030429906</v>
+        <v>-1.469263812449352</v>
       </c>
       <c r="G35">
-        <v>-9.240872578439726</v>
+        <v>-12.76348835441109</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.184544020802738</v>
       </c>
       <c r="E36">
-        <v>-33.28482492149164</v>
+        <v>-36.16501590290213</v>
       </c>
       <c r="F36">
-        <v>-0.951669209586317</v>
+        <v>-1.510098183570353</v>
       </c>
       <c r="G36">
-        <v>-9.129965992328602</v>
+        <v>-12.29299362236987</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.559595891584151</v>
       </c>
       <c r="E37">
-        <v>-32.3081825176794</v>
+        <v>-35.93810992003679</v>
       </c>
       <c r="F37">
-        <v>-0.6447789676667673</v>
+        <v>-1.286530933596198</v>
       </c>
       <c r="G37">
-        <v>-9.066178400877925</v>
+        <v>-12.17036108395864</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.94065407421649</v>
       </c>
       <c r="E38">
-        <v>-32.28548354171595</v>
+        <v>-35.19579113951445</v>
       </c>
       <c r="F38">
-        <v>-0.8266677401364688</v>
+        <v>-1.464475020493768</v>
       </c>
       <c r="G38">
-        <v>-9.235777648854787</v>
+        <v>-12.61750984885692</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.318221956830397</v>
       </c>
       <c r="E39">
-        <v>-31.68846990667772</v>
+        <v>-34.5325825356691</v>
       </c>
       <c r="F39">
-        <v>-0.7259904511024252</v>
+        <v>-1.25696567262288</v>
       </c>
       <c r="G39">
-        <v>-9.243775926877667</v>
+        <v>-12.64087898981864</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.69124570511836</v>
       </c>
       <c r="E40">
-        <v>-31.3132065868471</v>
+        <v>-34.33242172029307</v>
       </c>
       <c r="F40">
-        <v>-0.7713187153836142</v>
+        <v>-1.229925275493296</v>
       </c>
       <c r="G40">
-        <v>-9.454545119180906</v>
+        <v>-12.36098560665542</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.055599132394939</v>
       </c>
       <c r="E41">
-        <v>-30.44799860717861</v>
+        <v>-34.00242729088012</v>
       </c>
       <c r="F41">
-        <v>-0.6257637939355046</v>
+        <v>-1.137692363763391</v>
       </c>
       <c r="G41">
-        <v>-9.389271092783096</v>
+        <v>-12.4832440534207</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.401541892778116</v>
       </c>
       <c r="E42">
-        <v>-29.53456917203944</v>
+        <v>-33.33157462290983</v>
       </c>
       <c r="F42">
-        <v>-0.5755970356545638</v>
+        <v>-1.11702956726796</v>
       </c>
       <c r="G42">
-        <v>-9.297039294059001</v>
+        <v>-12.7241723155867</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.733157805214262</v>
       </c>
       <c r="E43">
-        <v>-29.24145010647095</v>
+        <v>-32.62229106027344</v>
       </c>
       <c r="F43">
-        <v>-0.3743915637189807</v>
+        <v>-1.024557257358645</v>
       </c>
       <c r="G43">
-        <v>-9.288620576752635</v>
+        <v>-12.95606609897603</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.052568886449307</v>
       </c>
       <c r="E44">
-        <v>-29.10271124829795</v>
+        <v>-32.37764478048305</v>
       </c>
       <c r="F44">
-        <v>-0.4170251488388629</v>
+        <v>-0.8709282388354491</v>
       </c>
       <c r="G44">
-        <v>-9.55337152461923</v>
+        <v>-12.66795594178434</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.353893328355099</v>
       </c>
       <c r="E45">
-        <v>-27.99460724404304</v>
+        <v>-31.94048401367859</v>
       </c>
       <c r="F45">
-        <v>-0.5178656262512579</v>
+        <v>-0.9415515301285238</v>
       </c>
       <c r="G45">
-        <v>-9.322315309251337</v>
+        <v>-12.75484452000805</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.642903489867326</v>
       </c>
       <c r="E46">
-        <v>-27.83203502716767</v>
+        <v>-31.61445199902235</v>
       </c>
       <c r="F46">
-        <v>-0.2989322635283626</v>
+        <v>-0.8660814611616693</v>
       </c>
       <c r="G46">
-        <v>-9.994329569359074</v>
+        <v>-12.76417363733771</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.926644112176082</v>
       </c>
       <c r="E47">
-        <v>-27.09664707611407</v>
+        <v>-30.80619184423732</v>
       </c>
       <c r="F47">
-        <v>-0.258287588542602</v>
+        <v>-1.113749232352874</v>
       </c>
       <c r="G47">
-        <v>-9.29018315424717</v>
+        <v>-12.96502774575084</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.204308253047223</v>
       </c>
       <c r="E48">
-        <v>-26.47820696630855</v>
+        <v>-30.18422631741683</v>
       </c>
       <c r="F48">
-        <v>-0.0592375285891032</v>
+        <v>-0.9585330618859137</v>
       </c>
       <c r="G48">
-        <v>-9.430345031288834</v>
+        <v>-12.92580771274709</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.477832045003439</v>
       </c>
       <c r="E49">
-        <v>-26.21442788383576</v>
+        <v>-29.93272619221583</v>
       </c>
       <c r="F49">
-        <v>-0.07177901106748771</v>
+        <v>-0.9020665695066826</v>
       </c>
       <c r="G49">
-        <v>-9.349915327412241</v>
+        <v>-12.66649930174706</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.758387803537089</v>
       </c>
       <c r="E50">
-        <v>-25.07345168675917</v>
+        <v>-29.71594134875765</v>
       </c>
       <c r="F50">
-        <v>-0.1235246376181644</v>
+        <v>-0.7819582663051711</v>
       </c>
       <c r="G50">
-        <v>-9.485651005067899</v>
+        <v>-12.90880806140293</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.047411405742341</v>
       </c>
       <c r="E51">
-        <v>-24.81253459985922</v>
+        <v>-28.72943366431969</v>
       </c>
       <c r="F51">
-        <v>0.02866882019598034</v>
+        <v>-0.9500008776370787</v>
       </c>
       <c r="G51">
-        <v>-9.512072469016822</v>
+        <v>-12.90734148972904</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.339349237196117</v>
       </c>
       <c r="E52">
-        <v>-24.22769576719062</v>
+        <v>-28.87175454543275</v>
       </c>
       <c r="F52">
-        <v>-0.2878114311457792</v>
+        <v>-0.8433800524879488</v>
       </c>
       <c r="G52">
-        <v>-9.358933253461215</v>
+        <v>-13.14817705661994</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.644626985683534</v>
       </c>
       <c r="E53">
-        <v>-23.4270026924724</v>
+        <v>-28.34184157400319</v>
       </c>
       <c r="F53">
-        <v>-0.0196896120446492</v>
+        <v>-0.716021877777136</v>
       </c>
       <c r="G53">
-        <v>-9.446728921162688</v>
+        <v>-13.20973665092269</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.96368399570531</v>
       </c>
       <c r="E54">
-        <v>-23.49614796209552</v>
+        <v>-27.62237573756055</v>
       </c>
       <c r="F54">
-        <v>0.1082558751547484</v>
+        <v>-0.7298266205447898</v>
       </c>
       <c r="G54">
-        <v>-9.553662852626687</v>
+        <v>-13.06673432580833</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.283110110578741</v>
       </c>
       <c r="E55">
-        <v>-22.9959598940523</v>
+        <v>-27.01253972836961</v>
       </c>
       <c r="F55">
-        <v>-0.1027574668299808</v>
+        <v>-0.749211246137701</v>
       </c>
       <c r="G55">
-        <v>-9.62732249087547</v>
+        <v>-13.34537963330324</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.608604936832911</v>
       </c>
       <c r="E56">
-        <v>-22.28987116982832</v>
+        <v>-27.16001854137741</v>
       </c>
       <c r="F56">
-        <v>-0.1405434459086803</v>
+        <v>-0.5931443423480658</v>
       </c>
       <c r="G56">
-        <v>-9.835661742752885</v>
+        <v>-13.1045738613222</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.937569040723087</v>
       </c>
       <c r="E57">
-        <v>-21.74841058967919</v>
+        <v>-26.3351841717243</v>
       </c>
       <c r="F57">
-        <v>0.1197859210343148</v>
+        <v>-0.8096638424592033</v>
       </c>
       <c r="G57">
-        <v>-9.926569323261271</v>
+        <v>-13.18935031149185</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.25244236950554</v>
       </c>
       <c r="E58">
-        <v>-21.29258345301511</v>
+        <v>-26.00898460352978</v>
       </c>
       <c r="F58">
-        <v>0.1445930396459515</v>
+        <v>-0.8624971154097558</v>
       </c>
       <c r="G58">
-        <v>-9.750958124585091</v>
+        <v>-13.33407412028663</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.54723825658105</v>
       </c>
       <c r="E59">
-        <v>-21.13072673503295</v>
+        <v>-25.51375521452496</v>
       </c>
       <c r="F59">
-        <v>-0.2913278507706631</v>
+        <v>-0.8410838180473886</v>
       </c>
       <c r="G59">
-        <v>-9.99429646390368</v>
+        <v>-13.36256136465206</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.81686996212209</v>
       </c>
       <c r="E60">
-        <v>-20.88086365318573</v>
+        <v>-25.60248160575724</v>
       </c>
       <c r="F60">
-        <v>-0.1660339676276266</v>
+        <v>-0.7466416504542169</v>
       </c>
       <c r="G60">
-        <v>-10.03472153548372</v>
+        <v>-13.37874331124802</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.04464608706959</v>
       </c>
       <c r="E61">
-        <v>-20.80889261578183</v>
+        <v>-25.85762941677141</v>
       </c>
       <c r="F61">
-        <v>-0.2502292304481684</v>
+        <v>-0.7683399062031472</v>
       </c>
       <c r="G61">
-        <v>-9.687739946967168</v>
+        <v>-13.4144343027069</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.21558621438701</v>
       </c>
       <c r="E62">
-        <v>-19.61614237537554</v>
+        <v>-25.09928663097293</v>
       </c>
       <c r="F62">
-        <v>-0.1860348985682207</v>
+        <v>-0.9259931335691435</v>
       </c>
       <c r="G62">
-        <v>-10.04408044772324</v>
+        <v>-13.19283300539917</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.32948699814467</v>
       </c>
       <c r="E63">
-        <v>-20.51374932233191</v>
+        <v>-25.09780129149841</v>
       </c>
       <c r="F63">
-        <v>-0.3004763403671808</v>
+        <v>-0.8464209892236257</v>
       </c>
       <c r="G63">
-        <v>-10.18942332853386</v>
+        <v>-13.35823448163223</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.37601274257897</v>
       </c>
       <c r="E64">
-        <v>-20.13735161976237</v>
+        <v>-24.92075154322052</v>
       </c>
       <c r="F64">
-        <v>-0.4578976248603933</v>
+        <v>-0.8651429208942975</v>
       </c>
       <c r="G64">
-        <v>-10.03549951368545</v>
+        <v>-13.38659261472163</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.34096502014215</v>
       </c>
       <c r="E65">
-        <v>-19.85666774381895</v>
+        <v>-25.09065988798831</v>
       </c>
       <c r="F65">
-        <v>-0.763961156111949</v>
+        <v>-1.00782257908729</v>
       </c>
       <c r="G65">
-        <v>-10.12521860834524</v>
+        <v>-13.51788388499082</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.23331833243336</v>
       </c>
       <c r="E66">
-        <v>-19.142921370048</v>
+        <v>-24.85105832824248</v>
       </c>
       <c r="F66">
-        <v>-0.5631748380821825</v>
+        <v>-1.205483466906294</v>
       </c>
       <c r="G66">
-        <v>-10.13868259705345</v>
+        <v>-13.50379420317568</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.05465694221974</v>
       </c>
       <c r="E67">
-        <v>-20.01336200143236</v>
+        <v>-24.58614712726777</v>
       </c>
       <c r="F67">
-        <v>-0.8836950372473952</v>
+        <v>-1.29139924882245</v>
       </c>
       <c r="G67">
-        <v>-10.14991196752266</v>
+        <v>-13.53878170370747</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.79851586062803</v>
       </c>
       <c r="E68">
-        <v>-19.43142139212866</v>
+        <v>-24.92297049548428</v>
       </c>
       <c r="F68">
-        <v>-0.7517352816140311</v>
+        <v>-1.533622161075054</v>
       </c>
       <c r="G68">
-        <v>-10.36983812878753</v>
+        <v>-12.90194530050002</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.48109981332668</v>
       </c>
       <c r="E69">
-        <v>-19.31682382889056</v>
+        <v>-24.56901591009675</v>
       </c>
       <c r="F69">
-        <v>-1.042342305496751</v>
+        <v>-1.416779282175378</v>
       </c>
       <c r="G69">
-        <v>-9.710456910457648</v>
+        <v>-13.45189643602929</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.11652579570016</v>
       </c>
       <c r="E70">
-        <v>-19.6109210448447</v>
+        <v>-24.55225602779436</v>
       </c>
       <c r="F70">
-        <v>-1.180414584195372</v>
+        <v>-1.631082899484027</v>
       </c>
       <c r="G70">
-        <v>-9.778137703462509</v>
+        <v>-12.85693843389363</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.709610335389531</v>
       </c>
       <c r="E71">
-        <v>-19.13250587983035</v>
+        <v>-24.36365414232291</v>
       </c>
       <c r="F71">
-        <v>-1.078242920366679</v>
+        <v>-1.711620091853806</v>
       </c>
       <c r="G71">
-        <v>-9.416258660019235</v>
+        <v>-12.84248459206917</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.276147864672538</v>
       </c>
       <c r="E72">
-        <v>-19.81875988790074</v>
+        <v>-24.50832982991996</v>
       </c>
       <c r="F72">
-        <v>-1.482256755162262</v>
+        <v>-1.59640164143102</v>
       </c>
       <c r="G72">
-        <v>-9.710483394821962</v>
+        <v>-12.81491767936366</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.836990877035429</v>
       </c>
       <c r="E73">
-        <v>-19.17265985885637</v>
+        <v>-24.23437073787793</v>
       </c>
       <c r="F73">
-        <v>-1.376445244965667</v>
+        <v>-1.842836801926859</v>
       </c>
       <c r="G73">
-        <v>-9.676871425961741</v>
+        <v>-13.26775065095287</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.401088018574558</v>
       </c>
       <c r="E74">
-        <v>-19.18989523092956</v>
+        <v>-24.56931931785526</v>
       </c>
       <c r="F74">
-        <v>-1.622857211174228</v>
+        <v>-1.892702862840583</v>
       </c>
       <c r="G74">
-        <v>-9.269015526069071</v>
+        <v>-12.89424166103014</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.974795306625558</v>
       </c>
       <c r="E75">
-        <v>-19.21915822996713</v>
+        <v>-24.91245537883847</v>
       </c>
       <c r="F75">
-        <v>-1.562740932018262</v>
+        <v>-1.938564595729175</v>
       </c>
       <c r="G75">
-        <v>-9.235307551388212</v>
+        <v>-12.5335875194364</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.579545733055927</v>
       </c>
       <c r="E76">
-        <v>-19.96342651854977</v>
+        <v>-24.4549844061096</v>
       </c>
       <c r="F76">
-        <v>-1.86780793728425</v>
+        <v>-2.085816841985621</v>
       </c>
       <c r="G76">
-        <v>-8.858041092278405</v>
+        <v>-12.35960179862</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.22181340839817</v>
       </c>
       <c r="E77">
-        <v>-20.24353074982022</v>
+        <v>-24.75973712140379</v>
       </c>
       <c r="F77">
-        <v>-2.007082177084333</v>
+        <v>-2.305715252732778</v>
       </c>
       <c r="G77">
-        <v>-8.993833049208233</v>
+        <v>-12.45450189704875</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.899014161163309</v>
       </c>
       <c r="E78">
-        <v>-19.7565703543534</v>
+        <v>-24.87457469376431</v>
       </c>
       <c r="F78">
-        <v>-2.049197204210063</v>
+        <v>-2.239334030909439</v>
       </c>
       <c r="G78">
-        <v>-8.676772171275612</v>
+        <v>-12.18447725013809</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.626005659121542</v>
       </c>
       <c r="E79">
-        <v>-20.19562402329307</v>
+        <v>-25.45906483393432</v>
       </c>
       <c r="F79">
-        <v>-1.98711106737024</v>
+        <v>-2.44305691138213</v>
       </c>
       <c r="G79">
-        <v>-8.864956821909944</v>
+        <v>-12.42292591369518</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.404849410105106</v>
       </c>
       <c r="E80">
-        <v>-21.47339183471936</v>
+        <v>-25.35097468784524</v>
       </c>
       <c r="F80">
-        <v>-2.100785440954208</v>
+        <v>-2.380074481012478</v>
       </c>
       <c r="G80">
-        <v>-8.272137432192652</v>
+        <v>-12.01924461172753</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.224966879707218</v>
       </c>
       <c r="E81">
-        <v>-21.40930487056281</v>
+        <v>-26.10052317712083</v>
       </c>
       <c r="F81">
-        <v>-2.311682811502545</v>
+        <v>-2.446540196310902</v>
       </c>
       <c r="G81">
-        <v>-8.131813338419564</v>
+        <v>-11.85358822348794</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.093518849553456</v>
       </c>
       <c r="E82">
-        <v>-21.36072792988253</v>
+        <v>-25.91198016181147</v>
       </c>
       <c r="F82">
-        <v>-1.982206303978264</v>
+        <v>-2.571667577605976</v>
       </c>
       <c r="G82">
-        <v>-8.520143640721614</v>
+        <v>-12.1791836878208</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.012844713570098</v>
       </c>
       <c r="E83">
-        <v>-21.98443918343298</v>
+        <v>-26.76432048258717</v>
       </c>
       <c r="F83">
-        <v>-2.288515031981049</v>
+        <v>-2.553363143106315</v>
       </c>
       <c r="G83">
-        <v>-7.990366969708663</v>
+        <v>-11.97789589794203</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.973599411720259</v>
       </c>
       <c r="E84">
-        <v>-22.98979664092786</v>
+        <v>-27.4877940185266</v>
       </c>
       <c r="F84">
-        <v>-2.761487967957482</v>
+        <v>-2.489925939032526</v>
       </c>
       <c r="G84">
-        <v>-8.07628224754383</v>
+        <v>-11.99454794200457</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.975314028486063</v>
       </c>
       <c r="E85">
-        <v>-23.68347281789681</v>
+        <v>-28.03891836220809</v>
       </c>
       <c r="F85">
-        <v>-2.338567475560403</v>
+        <v>-2.63371560954527</v>
       </c>
       <c r="G85">
-        <v>-7.867817194935923</v>
+        <v>-11.84453388143803</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.023023288269476</v>
       </c>
       <c r="E86">
-        <v>-24.3601083471749</v>
+        <v>-28.93073339090865</v>
       </c>
       <c r="F86">
-        <v>-2.524785296077135</v>
+        <v>-2.77774384987002</v>
       </c>
       <c r="G86">
-        <v>-7.798524166253437</v>
+        <v>-12.00087439453011</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.110949922301365</v>
       </c>
       <c r="E87">
-        <v>-25.82495647680607</v>
+        <v>-29.95914304533958</v>
       </c>
       <c r="F87">
-        <v>-2.542403842367277</v>
+        <v>-2.82870335575544</v>
       </c>
       <c r="G87">
-        <v>-8.120137044302554</v>
+        <v>-11.75348063692592</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.232813634536422</v>
       </c>
       <c r="E88">
-        <v>-26.46147425485021</v>
+        <v>-30.3989937257046</v>
       </c>
       <c r="F88">
-        <v>-2.619148768767041</v>
+        <v>-2.757052888882894</v>
       </c>
       <c r="G88">
-        <v>-7.733160755126067</v>
+        <v>-11.6199067455074</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.39765494604073</v>
       </c>
       <c r="E89">
-        <v>-27.65646156141629</v>
+        <v>-31.56927141384783</v>
       </c>
       <c r="F89">
-        <v>-2.640635790828257</v>
+        <v>-2.991188450181966</v>
       </c>
       <c r="G89">
-        <v>-7.198547377080242</v>
+        <v>-11.7449394294346</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.602946809849607</v>
       </c>
       <c r="E90">
-        <v>-28.8049504968716</v>
+        <v>-32.59284012956456</v>
       </c>
       <c r="F90">
-        <v>-2.467178141784249</v>
+        <v>-3.053088204356159</v>
       </c>
       <c r="G90">
-        <v>-7.918845943878249</v>
+        <v>-11.98897298331643</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.83790023383581</v>
       </c>
       <c r="E91">
-        <v>-30.30349726583085</v>
+        <v>-33.68530278459697</v>
       </c>
       <c r="F91">
-        <v>-2.725092817748084</v>
+        <v>-2.854161571145677</v>
       </c>
       <c r="G91">
-        <v>-7.810329571646479</v>
+        <v>-11.76463717539326</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.106605929490832</v>
       </c>
       <c r="E92">
-        <v>-31.52251491971863</v>
+        <v>-35.23724026210665</v>
       </c>
       <c r="F92">
-        <v>-2.938119092521616</v>
+        <v>-3.251366225890248</v>
       </c>
       <c r="G92">
-        <v>-7.972069584513112</v>
+        <v>-12.18948941608455</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.402445549028331</v>
       </c>
       <c r="E93">
-        <v>-32.47754970980328</v>
+        <v>-35.71770003313546</v>
       </c>
       <c r="F93">
-        <v>-3.01304161063522</v>
+        <v>-3.309026395696914</v>
       </c>
       <c r="G93">
-        <v>-8.532098020663922</v>
+        <v>-12.3508089896677</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.704456038857118</v>
       </c>
       <c r="E94">
-        <v>-34.06076988575794</v>
+        <v>-37.05043219782985</v>
       </c>
       <c r="F94">
-        <v>-2.960211651154278</v>
+        <v>-3.469014790771402</v>
       </c>
       <c r="G94">
-        <v>-8.748971858941578</v>
+        <v>-12.15126916783367</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.007733780992472</v>
       </c>
       <c r="E95">
-        <v>-35.90903938114455</v>
+        <v>-38.65698080763503</v>
       </c>
       <c r="F95">
-        <v>-3.146306044927993</v>
+        <v>-3.447828466077401</v>
       </c>
       <c r="G95">
-        <v>-8.768533872533132</v>
+        <v>-12.07254770545534</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.300477827241851</v>
       </c>
       <c r="E96">
-        <v>-37.41859260617944</v>
+        <v>-40.57598506702146</v>
       </c>
       <c r="F96">
-        <v>-3.306071609171128</v>
+        <v>-3.690589817141825</v>
       </c>
       <c r="G96">
-        <v>-8.78334194273029</v>
+        <v>-12.45297904610069</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.562460554051569</v>
       </c>
       <c r="E97">
-        <v>-39.17842779690726</v>
+        <v>-42.11837878555997</v>
       </c>
       <c r="F97">
-        <v>-3.363906564499784</v>
+        <v>-3.903582957219245</v>
       </c>
       <c r="G97">
-        <v>-9.240505107884868</v>
+        <v>-12.98899609545516</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.778806197604311</v>
       </c>
       <c r="E98">
-        <v>-40.64981504300551</v>
+        <v>-43.22859305870246</v>
       </c>
       <c r="F98">
-        <v>-3.446864246420543</v>
+        <v>-3.825356909903276</v>
       </c>
       <c r="G98">
-        <v>-9.472047973447033</v>
+        <v>-12.79782202219887</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.948909755133151</v>
       </c>
       <c r="E99">
-        <v>-42.99950435136542</v>
+        <v>-45.05725426163585</v>
       </c>
       <c r="F99">
-        <v>-3.499504509766243</v>
+        <v>-4.034311758892049</v>
       </c>
       <c r="G99">
-        <v>-9.374982778235601</v>
+        <v>-13.46202008428839</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.055099608613649</v>
       </c>
       <c r="E100">
-        <v>-44.48317508320947</v>
+        <v>-46.71118203074629</v>
       </c>
       <c r="F100">
-        <v>-3.749171959867806</v>
+        <v>-4.101399578109975</v>
       </c>
       <c r="G100">
-        <v>-9.613305641062196</v>
+        <v>-13.76814954085033</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.094169506943873</v>
       </c>
       <c r="E101">
-        <v>-46.94585887500879</v>
+        <v>-48.75118937985467</v>
       </c>
       <c r="F101">
-        <v>-3.696578913464065</v>
+        <v>-4.423050498780009</v>
       </c>
       <c r="G101">
-        <v>-10.7284629059657</v>
+        <v>-13.92919764969926</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.055509798596882</v>
       </c>
       <c r="E102">
-        <v>-49.02287291370784</v>
+        <v>-50.77600143443031</v>
       </c>
       <c r="F102">
-        <v>-3.871460526073486</v>
+        <v>-4.520246987987489</v>
       </c>
       <c r="G102">
-        <v>-10.64913561375368</v>
+        <v>-13.89889953692385</v>
       </c>
     </row>
   </sheetData>
